--- a/data/gini.xlsx
+++ b/data/gini.xlsx
@@ -34136,4 +34136,10 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/DataMashup"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{e782e157-8ece-4105-b8e9-fe1eecbfcd69}" enabled="1" method="Privileged" siteId="{eb5b2d6e-028e-454d-b878-0c055adbeb2a}" removed="0"/>
+</clbl:labelList>
 </file>